--- a/samples/DataMappingRegistry-sample.xlsx
+++ b/samples/DataMappingRegistry-sample.xlsx
@@ -25,7 +25,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2">'Datasets'!A1:I45</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3">'Attributes'!A1:I278</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4">'Mappings'!A1:J218</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5">'Flows'!A1:I46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5">'Flows'!A1:J46</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6">'Events'!A1:L10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7">'BusinessTerms'!A1:H32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9">'GQL Schema'!A1:I21</definedName>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G18" t="str" xml:space="preserve">
         <v xml:space="preserve">{
-  field: String!
+  field: String
 }</v>
       </c>
       <c r="H18" t="str">
@@ -14424,7 +14424,7 @@
       <formula1>Domains!$A$2:$A$1000</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" sqref="D2:D1000">
-      <formula1>"01-Domain service,02-Orchestrator service,03-Integration service,04-BFF,05-FedGQL router,06-Frontend,07-Core system,08-Third party"</formula1>
+      <formula1>"01-Domain service,02-Orchestrator service,03-Integration service,04-BFF,05-FedGQL router,06-Frontend,07-Core system,08-Third party,09-Data hub,10-Data platform"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" sqref="I2:I1000">
       <formula1>"Draft,Proposed,Approved,Deprecated"</formula1>
@@ -30896,17 +30896,18 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:J46"/>
   <cols>
     <col min="1" max="1" width="21.83203125" customWidth="1"/>
     <col min="2" max="2" width="33.83203125" customWidth="1"/>
     <col min="3" max="3" width="19.83203125" customWidth="1"/>
     <col min="4" max="4" width="19.83203125" customWidth="1"/>
     <col min="5" max="5" width="19.83203125" customWidth="1"/>
-    <col min="6" max="6" width="26.83203125" customWidth="1"/>
-    <col min="7" max="7" width="19.83203125" customWidth="1"/>
-    <col min="8" max="8" width="37.83203125" customWidth="1"/>
-    <col min="9" max="9" width="19.83203125" customWidth="1"/>
+    <col min="6" max="6" width="24.83203125" customWidth="1"/>
+    <col min="7" max="7" width="26.83203125" customWidth="1"/>
+    <col min="8" max="8" width="19.83203125" customWidth="1"/>
+    <col min="9" max="9" width="37.83203125" customWidth="1"/>
+    <col min="10" max="10" width="19.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -30926,15 +30927,18 @@
         <v>Pattern</v>
       </c>
       <c r="F1" t="str">
+        <v>MappingType</v>
+      </c>
+      <c r="G1" t="str">
         <v>Middleware</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>Frequency</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>Description</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>Status</v>
       </c>
     </row>
@@ -30955,15 +30959,18 @@
         <v>CDC</v>
       </c>
       <c r="F2" t="str">
+        <v>Domain data mapping</v>
+      </c>
+      <c r="G2" t="str">
         <v>Kafka Connect JDBC source + SMTs</v>
       </c>
-      <c r="G2" t="str">
+      <c r="H2" t="str">
         <v>Near real-time</v>
       </c>
-      <c r="H2" t="str">
+      <c r="I2" t="str">
         <v>Change data capture on C_B_PRODUCT.</v>
       </c>
-      <c r="I2" t="str">
+      <c r="J2" t="str">
         <v>Approved</v>
       </c>
     </row>
@@ -30984,15 +30991,18 @@
         <v>Kafka event</v>
       </c>
       <c r="F3" t="str">
+        <v>Domain data mapping</v>
+      </c>
+      <c r="G3" t="str">
         <v>Kafka Streams consumer</v>
       </c>
-      <c r="G3" t="str">
+      <c r="H3" t="str">
         <v>Real-time</v>
       </c>
-      <c r="H3" t="str">
+      <c r="I3" t="str">
         <v>Integration service consumes mdm.product.golden.v1.</v>
       </c>
-      <c r="I3" t="str">
+      <c r="J3" t="str">
         <v>Approved</v>
       </c>
     </row>
@@ -31013,15 +31023,18 @@
         <v>REST API</v>
       </c>
       <c r="F4" t="str">
+        <v>Domain data mapping</v>
+      </c>
+      <c r="G4" t="str">
         <v>Akeneo REST API, delta poll</v>
       </c>
-      <c r="G4" t="str">
+      <c r="H4" t="str">
         <v>Every 5 min</v>
       </c>
-      <c r="H4" t="str">
+      <c r="I4" t="str">
         <v>Reads products updated since the last poll.</v>
       </c>
-      <c r="I4" t="str">
+      <c r="J4" t="str">
         <v>Proposed</v>
       </c>
     </row>
@@ -31042,15 +31055,18 @@
         <v>File (CSV)</v>
       </c>
       <c r="F5" t="str">
+        <v>Domain data mapping</v>
+      </c>
+      <c r="G5" t="str">
         <v>SFTP + Spring Batch</v>
       </c>
-      <c r="G5" t="str">
+      <c r="H5" t="str">
         <v>Daily 02:00</v>
       </c>
-      <c r="H5" t="str">
+      <c r="I5" t="str">
         <v>Supplier logistics extract joined by GTIN.</v>
       </c>
-      <c r="I5" t="str">
+      <c r="J5" t="str">
         <v>Proposed</v>
       </c>
     </row>
@@ -31071,15 +31087,18 @@
         <v>Internal</v>
       </c>
       <c r="F6" t="str">
+        <v>Domain data mapping</v>
+      </c>
+      <c r="G6" t="str">
         <v>Databricks Auto Loader (Kafka source)</v>
       </c>
-      <c r="G6" t="str">
+      <c r="H6" t="str">
         <v>Streaming</v>
       </c>
-      <c r="H6" t="str">
+      <c r="I6" t="str">
         <v>Lands product.ingested.v1 in the bronze Delta table for analytics.</v>
       </c>
-      <c r="I6" t="str">
+      <c r="J6" t="str">
         <v>Proposed</v>
       </c>
     </row>
@@ -31100,15 +31119,18 @@
         <v>Kafka event</v>
       </c>
       <c r="F7" t="str">
+        <v>Domain data mapping</v>
+      </c>
+      <c r="G7" t="str">
         <v>Spring Kafka consumer</v>
       </c>
-      <c r="G7" t="str">
+      <c r="H7" t="str">
         <v>Real-time</v>
       </c>
-      <c r="H7" t="str">
+      <c r="I7" t="str">
         <v>Product Service upserts the canonical product.</v>
       </c>
-      <c r="I7" t="str">
+      <c r="J7" t="str">
         <v>Approved</v>
       </c>
     </row>
@@ -31129,15 +31151,18 @@
         <v>Internal</v>
       </c>
       <c r="F8" t="str">
+        <v>API data mapping</v>
+      </c>
+      <c r="G8" t="str">
         <v>Spring Data JPA + MapStruct</v>
       </c>
-      <c r="G8" t="str">
+      <c r="H8" t="str">
         <v>On request</v>
       </c>
-      <c r="H8" t="str">
+      <c r="I8" t="str">
         <v>Entity → REST DTO.</v>
       </c>
-      <c r="I8" t="str">
+      <c r="J8" t="str">
         <v>Approved</v>
       </c>
     </row>
@@ -31158,15 +31183,18 @@
         <v>Internal</v>
       </c>
       <c r="F9" t="str">
+        <v>API data mapping</v>
+      </c>
+      <c r="G9" t="str">
         <v>DGS data fetchers</v>
       </c>
-      <c r="G9" t="str">
+      <c r="H9" t="str">
         <v>On request</v>
       </c>
-      <c r="H9" t="str">
+      <c r="I9" t="str">
         <v>Entity → GraphQL type.</v>
       </c>
-      <c r="I9" t="str">
+      <c r="J9" t="str">
         <v>Approved</v>
       </c>
     </row>
@@ -31187,15 +31215,18 @@
         <v>Internal</v>
       </c>
       <c r="F10" t="str">
+        <v>Domain data mapping</v>
+      </c>
+      <c r="G10" t="str">
         <v>Debezium outbox event router</v>
       </c>
-      <c r="G10" t="str">
+      <c r="H10" t="str">
         <v>Real-time</v>
       </c>
-      <c r="H10" t="str">
+      <c r="I10" t="str">
         <v>Transactional outbox.</v>
       </c>
-      <c r="I10" t="str">
+      <c r="J10" t="str">
         <v>Approved</v>
       </c>
     </row>
@@ -31216,15 +31247,18 @@
         <v>Kafka event</v>
       </c>
       <c r="F11" t="str">
+        <v>Domain data mapping</v>
+      </c>
+      <c r="G11" t="str">
         <v>Kafka consumer → Elasticsearch bulk</v>
       </c>
-      <c r="G11" t="str">
+      <c r="H11" t="str">
         <v>Real-time</v>
       </c>
-      <c r="H11" t="str">
+      <c r="I11" t="str">
         <v>Keeps idx_products in sync.</v>
       </c>
-      <c r="I11" t="str">
+      <c r="J11" t="str">
         <v>Proposed</v>
       </c>
     </row>
@@ -31245,15 +31279,18 @@
         <v>GraphQL</v>
       </c>
       <c r="F12" t="str">
+        <v>API data mapping</v>
+      </c>
+      <c r="G12" t="str">
         <v>Federation 2 composition</v>
       </c>
-      <c r="G12" t="str">
+      <c r="H12" t="str">
         <v>On request</v>
       </c>
-      <c r="H12" t="str">
+      <c r="I12" t="str">
         <v>Router fetches product fields from the product subgraph.</v>
       </c>
-      <c r="I12" t="str">
+      <c r="J12" t="str">
         <v>Approved</v>
       </c>
     </row>
@@ -31274,15 +31311,18 @@
         <v>GraphQL</v>
       </c>
       <c r="F13" t="str">
+        <v>API data mapping</v>
+      </c>
+      <c r="G13" t="str">
         <v>Apollo Client</v>
       </c>
-      <c r="G13" t="str">
+      <c r="H13" t="str">
         <v>On request</v>
       </c>
-      <c r="H13" t="str">
+      <c r="I13" t="str">
         <v>PDP query + view-model mapping.</v>
       </c>
-      <c r="I13" t="str">
+      <c r="J13" t="str">
         <v>Approved</v>
       </c>
     </row>
@@ -31303,15 +31343,18 @@
         <v>REST API</v>
       </c>
       <c r="F14" t="str">
+        <v>API data mapping</v>
+      </c>
+      <c r="G14" t="str">
         <v>BFF HTTP client</v>
       </c>
-      <c r="G14" t="str">
+      <c r="H14" t="str">
         <v>On request</v>
       </c>
-      <c r="H14" t="str">
+      <c r="I14" t="str">
         <v>BFF composes the app's product screen.</v>
       </c>
-      <c r="I14" t="str">
+      <c r="J14" t="str">
         <v>Approved</v>
       </c>
     </row>
@@ -31332,15 +31375,18 @@
         <v>REST API</v>
       </c>
       <c r="F15" t="str">
+        <v>API data mapping</v>
+      </c>
+      <c r="G15" t="str">
         <v>fetch</v>
       </c>
-      <c r="G15" t="str">
+      <c r="H15" t="str">
         <v>On request</v>
       </c>
-      <c r="H15" t="str">
-        <v/>
-      </c>
       <c r="I15" t="str">
+        <v/>
+      </c>
+      <c r="J15" t="str">
         <v>Approved</v>
       </c>
     </row>
@@ -31361,15 +31407,18 @@
         <v>GraphQL</v>
       </c>
       <c r="F16" t="str">
+        <v>API data mapping</v>
+      </c>
+      <c r="G16" t="str">
         <v>Apollo Client</v>
       </c>
-      <c r="G16" t="str">
+      <c r="H16" t="str">
         <v>On request</v>
       </c>
-      <c r="H16" t="str">
+      <c r="I16" t="str">
         <v>Add to cart from PDP.</v>
       </c>
-      <c r="I16" t="str">
+      <c r="J16" t="str">
         <v>Approved</v>
       </c>
     </row>
@@ -31390,15 +31439,18 @@
         <v>GraphQL</v>
       </c>
       <c r="F17" t="str">
+        <v>API data mapping</v>
+      </c>
+      <c r="G17" t="str">
         <v>Router query plan</v>
       </c>
-      <c r="G17" t="str">
+      <c r="H17" t="str">
         <v>On request</v>
       </c>
-      <c r="H17" t="str">
-        <v/>
-      </c>
       <c r="I17" t="str">
+        <v/>
+      </c>
+      <c r="J17" t="str">
         <v>Approved</v>
       </c>
     </row>
@@ -31419,15 +31471,18 @@
         <v>Internal</v>
       </c>
       <c r="F18" t="str">
+        <v>API data mapping</v>
+      </c>
+      <c r="G18" t="str">
         <v>Mongoose</v>
       </c>
-      <c r="G18" t="str">
+      <c r="H18" t="str">
         <v>On request</v>
       </c>
-      <c r="H18" t="str">
+      <c r="I18" t="str">
         <v>Mutation input → document.</v>
       </c>
-      <c r="I18" t="str">
+      <c r="J18" t="str">
         <v>Approved</v>
       </c>
     </row>
@@ -31448,15 +31503,18 @@
         <v>Internal</v>
       </c>
       <c r="F19" t="str">
+        <v>Domain data mapping</v>
+      </c>
+      <c r="G19" t="str">
         <v>MongoDB change stream → Kafka</v>
       </c>
-      <c r="G19" t="str">
+      <c r="H19" t="str">
         <v>Real-time</v>
       </c>
-      <c r="H19" t="str">
-        <v/>
-      </c>
       <c r="I19" t="str">
+        <v/>
+      </c>
+      <c r="J19" t="str">
         <v>Approved</v>
       </c>
     </row>
@@ -31477,15 +31535,18 @@
         <v>Internal</v>
       </c>
       <c r="F20" t="str">
+        <v>API data mapping</v>
+      </c>
+      <c r="G20" t="str">
         <v>Spring Data JPA</v>
       </c>
-      <c r="G20" t="str">
+      <c r="H20" t="str">
         <v>On request</v>
       </c>
-      <c r="H20" t="str">
+      <c r="I20" t="str">
         <v>Entity → REST DTO.</v>
       </c>
-      <c r="I20" t="str">
+      <c r="J20" t="str">
         <v>Approved</v>
       </c>
     </row>
@@ -31506,15 +31567,18 @@
         <v>Internal</v>
       </c>
       <c r="F21" t="str">
+        <v>API data mapping</v>
+      </c>
+      <c r="G21" t="str">
         <v>DGS data fetchers</v>
       </c>
-      <c r="G21" t="str">
+      <c r="H21" t="str">
         <v>On request</v>
       </c>
-      <c r="H21" t="str">
+      <c r="I21" t="str">
         <v>Entity → GraphQL type.</v>
       </c>
-      <c r="I21" t="str">
+      <c r="J21" t="str">
         <v>Approved</v>
       </c>
     </row>
@@ -31535,15 +31599,18 @@
         <v>Internal</v>
       </c>
       <c r="F22" t="str">
+        <v>Domain data mapping</v>
+      </c>
+      <c r="G22" t="str">
         <v>Debezium outbox event router</v>
       </c>
-      <c r="G22" t="str">
+      <c r="H22" t="str">
         <v>Real-time</v>
       </c>
-      <c r="H22" t="str">
+      <c r="I22" t="str">
         <v>Transactional outbox.</v>
       </c>
-      <c r="I22" t="str">
+      <c r="J22" t="str">
         <v>Approved</v>
       </c>
     </row>
@@ -31564,15 +31631,18 @@
         <v>GraphQL</v>
       </c>
       <c r="F23" t="str">
+        <v>API data mapping</v>
+      </c>
+      <c r="G23" t="str">
         <v>Federation 2 composition</v>
       </c>
-      <c r="G23" t="str">
+      <c r="H23" t="str">
         <v>On request</v>
       </c>
-      <c r="H23" t="str">
+      <c r="I23" t="str">
         <v>Router fetches store price from the pnp subgraph.</v>
       </c>
-      <c r="I23" t="str">
+      <c r="J23" t="str">
         <v>Approved</v>
       </c>
     </row>
@@ -31593,15 +31663,18 @@
         <v>Internal</v>
       </c>
       <c r="F24" t="str">
+        <v>API data mapping</v>
+      </c>
+      <c r="G24" t="str">
         <v>sqlc</v>
       </c>
-      <c r="G24" t="str">
+      <c r="H24" t="str">
         <v>On request</v>
       </c>
-      <c r="H24" t="str">
+      <c r="I24" t="str">
         <v>Entity → REST DTO (get + reserve).</v>
       </c>
-      <c r="I24" t="str">
+      <c r="J24" t="str">
         <v>Approved</v>
       </c>
     </row>
@@ -31622,15 +31695,18 @@
         <v>Internal</v>
       </c>
       <c r="F25" t="str">
+        <v>API data mapping</v>
+      </c>
+      <c r="G25" t="str">
         <v>gqlgen resolvers</v>
       </c>
-      <c r="G25" t="str">
+      <c r="H25" t="str">
         <v>On request</v>
       </c>
-      <c r="H25" t="str">
+      <c r="I25" t="str">
         <v>Entity → GraphQL type.</v>
       </c>
-      <c r="I25" t="str">
+      <c r="J25" t="str">
         <v>Approved</v>
       </c>
     </row>
@@ -31651,15 +31727,18 @@
         <v>Internal</v>
       </c>
       <c r="F26" t="str">
+        <v>API data mapping</v>
+      </c>
+      <c r="G26" t="str">
         <v>gRPC server</v>
       </c>
-      <c r="G26" t="str">
+      <c r="H26" t="str">
         <v>On request</v>
       </c>
-      <c r="H26" t="str">
+      <c r="I26" t="str">
         <v>Entity → protobuf messages (get + reserve).</v>
       </c>
-      <c r="I26" t="str">
+      <c r="J26" t="str">
         <v>Approved</v>
       </c>
     </row>
@@ -31680,15 +31759,18 @@
         <v>Internal</v>
       </c>
       <c r="F27" t="str">
+        <v>Domain data mapping</v>
+      </c>
+      <c r="G27" t="str">
         <v>Debezium outbox event router</v>
       </c>
-      <c r="G27" t="str">
+      <c r="H27" t="str">
         <v>Real-time</v>
       </c>
-      <c r="H27" t="str">
+      <c r="I27" t="str">
         <v>Transactional outbox.</v>
       </c>
-      <c r="I27" t="str">
+      <c r="J27" t="str">
         <v>Approved</v>
       </c>
     </row>
@@ -31709,15 +31791,18 @@
         <v>GraphQL</v>
       </c>
       <c r="F28" t="str">
+        <v>API data mapping</v>
+      </c>
+      <c r="G28" t="str">
         <v>Federation 2 composition</v>
       </c>
-      <c r="G28" t="str">
+      <c r="H28" t="str">
         <v>On request</v>
       </c>
-      <c r="H28" t="str">
+      <c r="I28" t="str">
         <v>Router fetches stock from the inventory subgraph.</v>
       </c>
-      <c r="I28" t="str">
+      <c r="J28" t="str">
         <v>Approved</v>
       </c>
     </row>
@@ -31738,15 +31823,18 @@
         <v>Internal</v>
       </c>
       <c r="F29" t="str">
+        <v>API data mapping</v>
+      </c>
+      <c r="G29" t="str">
         <v>Spring Data JPA</v>
       </c>
-      <c r="G29" t="str">
+      <c r="H29" t="str">
         <v>On request</v>
       </c>
-      <c r="H29" t="str">
+      <c r="I29" t="str">
         <v>Entity → REST DTO.</v>
       </c>
-      <c r="I29" t="str">
+      <c r="J29" t="str">
         <v>Approved</v>
       </c>
     </row>
@@ -31767,15 +31855,18 @@
         <v>Internal</v>
       </c>
       <c r="F30" t="str">
+        <v>API data mapping</v>
+      </c>
+      <c r="G30" t="str">
         <v>DGS data fetchers</v>
       </c>
-      <c r="G30" t="str">
+      <c r="H30" t="str">
         <v>On request</v>
       </c>
-      <c r="H30" t="str">
+      <c r="I30" t="str">
         <v>Entity → GraphQL type.</v>
       </c>
-      <c r="I30" t="str">
+      <c r="J30" t="str">
         <v>Approved</v>
       </c>
     </row>
@@ -31796,15 +31887,18 @@
         <v>Internal</v>
       </c>
       <c r="F31" t="str">
+        <v>Domain data mapping</v>
+      </c>
+      <c r="G31" t="str">
         <v>Debezium outbox event router</v>
       </c>
-      <c r="G31" t="str">
+      <c r="H31" t="str">
         <v>Real-time</v>
       </c>
-      <c r="H31" t="str">
+      <c r="I31" t="str">
         <v>Transactional outbox.</v>
       </c>
-      <c r="I31" t="str">
+      <c r="J31" t="str">
         <v>Approved</v>
       </c>
     </row>
@@ -31825,15 +31919,18 @@
         <v>GraphQL</v>
       </c>
       <c r="F32" t="str">
+        <v>API data mapping</v>
+      </c>
+      <c r="G32" t="str">
         <v>Federation 2 composition</v>
       </c>
-      <c r="G32" t="str">
+      <c r="H32" t="str">
         <v>On request</v>
       </c>
-      <c r="H32" t="str">
+      <c r="I32" t="str">
         <v>Router can read a PaymentTransaction by id.</v>
       </c>
-      <c r="I32" t="str">
+      <c r="J32" t="str">
         <v>Approved</v>
       </c>
     </row>
@@ -31854,15 +31951,18 @@
         <v>Internal</v>
       </c>
       <c r="F33" t="str">
+        <v>API data mapping</v>
+      </c>
+      <c r="G33" t="str">
         <v>Apollo resolvers</v>
       </c>
-      <c r="G33" t="str">
+      <c r="H33" t="str">
         <v>On request</v>
       </c>
-      <c r="H33" t="str">
+      <c r="I33" t="str">
         <v>Entity → GraphQL type.</v>
       </c>
-      <c r="I33" t="str">
+      <c r="J33" t="str">
         <v>Approved</v>
       </c>
     </row>
@@ -31883,15 +31983,18 @@
         <v>Internal</v>
       </c>
       <c r="F34" t="str">
+        <v>Domain data mapping</v>
+      </c>
+      <c r="G34" t="str">
         <v>Debezium outbox event router</v>
       </c>
-      <c r="G34" t="str">
+      <c r="H34" t="str">
         <v>Real-time</v>
       </c>
-      <c r="H34" t="str">
+      <c r="I34" t="str">
         <v>Transactional outbox.</v>
       </c>
-      <c r="I34" t="str">
+      <c r="J34" t="str">
         <v>Approved</v>
       </c>
     </row>
@@ -31912,15 +32015,18 @@
         <v>GraphQL</v>
       </c>
       <c r="F35" t="str">
+        <v>API data mapping</v>
+      </c>
+      <c r="G35" t="str">
         <v>Federation 2 composition</v>
       </c>
-      <c r="G35" t="str">
+      <c r="H35" t="str">
         <v>On request</v>
       </c>
-      <c r="H35" t="str">
+      <c r="I35" t="str">
         <v>Router runs submitCheckout + order reads on the checkout subgraph.</v>
       </c>
-      <c r="I35" t="str">
+      <c r="J35" t="str">
         <v>Approved</v>
       </c>
     </row>
@@ -31941,15 +32047,18 @@
         <v>REST API</v>
       </c>
       <c r="F36" t="str">
+        <v>API data mapping</v>
+      </c>
+      <c r="G36" t="str">
         <v>Internal HTTP client</v>
       </c>
-      <c r="G36" t="str">
+      <c r="H36" t="str">
         <v>On checkout</v>
       </c>
-      <c r="H36" t="str">
+      <c r="I36" t="str">
         <v>Orchestrator reads then clears the cart over REST (constraint: a GQL subgraph must not call another GQL subgraph).</v>
       </c>
-      <c r="I36" t="str">
+      <c r="J36" t="str">
         <v>Approved</v>
       </c>
     </row>
@@ -31970,15 +32079,18 @@
         <v>REST API</v>
       </c>
       <c r="F37" t="str">
+        <v>API data mapping</v>
+      </c>
+      <c r="G37" t="str">
         <v>Internal HTTP client</v>
       </c>
-      <c r="G37" t="str">
+      <c r="H37" t="str">
         <v>On checkout</v>
       </c>
-      <c r="H37" t="str">
+      <c r="I37" t="str">
         <v>Orchestrator reserves stock per line over REST.</v>
       </c>
-      <c r="I37" t="str">
+      <c r="J37" t="str">
         <v>Approved</v>
       </c>
     </row>
@@ -31999,15 +32111,18 @@
         <v>REST API</v>
       </c>
       <c r="F38" t="str">
+        <v>API data mapping</v>
+      </c>
+      <c r="G38" t="str">
         <v>Internal HTTP client</v>
       </c>
-      <c r="G38" t="str">
+      <c r="H38" t="str">
         <v>On checkout</v>
       </c>
-      <c r="H38" t="str">
+      <c r="I38" t="str">
         <v>Orchestrator authorises + captures payment over REST.</v>
       </c>
-      <c r="I38" t="str">
+      <c r="J38" t="str">
         <v>Approved</v>
       </c>
     </row>
@@ -32028,15 +32143,18 @@
         <v>REST API</v>
       </c>
       <c r="F39" t="str">
+        <v>API data mapping</v>
+      </c>
+      <c r="G39" t="str">
         <v>Internal HTTP client</v>
       </c>
-      <c r="G39" t="str">
+      <c r="H39" t="str">
         <v>On cart read</v>
       </c>
-      <c r="H39" t="str">
+      <c r="I39" t="str">
         <v>Cart prices each line at read time from the store price (REST, never GQL→GQL).</v>
       </c>
-      <c r="I39" t="str">
+      <c r="J39" t="str">
         <v>Approved</v>
       </c>
     </row>
@@ -32057,15 +32175,18 @@
         <v>Internal</v>
       </c>
       <c r="F40" t="str">
+        <v>API data mapping</v>
+      </c>
+      <c r="G40" t="str">
         <v>Mongoose</v>
       </c>
-      <c r="G40" t="str">
+      <c r="H40" t="str">
         <v>On request</v>
       </c>
-      <c r="H40" t="str">
+      <c r="I40" t="str">
         <v>Document → REST DTO.</v>
       </c>
-      <c r="I40" t="str">
+      <c r="J40" t="str">
         <v>Approved</v>
       </c>
     </row>
@@ -32086,15 +32207,18 @@
         <v>Internal</v>
       </c>
       <c r="F41" t="str">
+        <v>API data mapping</v>
+      </c>
+      <c r="G41" t="str">
         <v>Apollo resolvers</v>
       </c>
-      <c r="G41" t="str">
+      <c r="H41" t="str">
         <v>On request</v>
       </c>
-      <c r="H41" t="str">
+      <c r="I41" t="str">
         <v>Document → GraphQL type.</v>
       </c>
-      <c r="I41" t="str">
+      <c r="J41" t="str">
         <v>Approved</v>
       </c>
     </row>
@@ -32115,15 +32239,18 @@
         <v>GraphQL</v>
       </c>
       <c r="F42" t="str">
+        <v>API data mapping</v>
+      </c>
+      <c r="G42" t="str">
         <v>Federation 2 composition</v>
       </c>
-      <c r="G42" t="str">
+      <c r="H42" t="str">
         <v>On request</v>
       </c>
-      <c r="H42" t="str">
+      <c r="I42" t="str">
         <v>Router fetches cart reads from the cart subgraph.</v>
       </c>
-      <c r="I42" t="str">
+      <c r="J42" t="str">
         <v>Approved</v>
       </c>
     </row>
@@ -32144,15 +32271,18 @@
         <v>Internal</v>
       </c>
       <c r="F43" t="str">
+        <v>API data mapping</v>
+      </c>
+      <c r="G43" t="str">
         <v>Resolver → Elasticsearch</v>
       </c>
-      <c r="G43" t="str">
+      <c r="H43" t="str">
         <v>On request</v>
       </c>
-      <c r="H43" t="str">
+      <c r="I43" t="str">
         <v>Index document → REST DTO.</v>
       </c>
-      <c r="I43" t="str">
+      <c r="J43" t="str">
         <v>Proposed</v>
       </c>
     </row>
@@ -32173,15 +32303,18 @@
         <v>Internal</v>
       </c>
       <c r="F44" t="str">
+        <v>API data mapping</v>
+      </c>
+      <c r="G44" t="str">
         <v>Resolver → Elasticsearch</v>
       </c>
-      <c r="G44" t="str">
+      <c r="H44" t="str">
         <v>On request</v>
       </c>
-      <c r="H44" t="str">
+      <c r="I44" t="str">
         <v>Index document → GraphQL type.</v>
       </c>
-      <c r="I44" t="str">
+      <c r="J44" t="str">
         <v>Proposed</v>
       </c>
     </row>
@@ -32202,15 +32335,18 @@
         <v>GraphQL</v>
       </c>
       <c r="F45" t="str">
+        <v>API data mapping</v>
+      </c>
+      <c r="G45" t="str">
         <v>Federation 2 composition</v>
       </c>
-      <c r="G45" t="str">
+      <c r="H45" t="str">
         <v>On request</v>
       </c>
-      <c r="H45" t="str">
+      <c r="I45" t="str">
         <v>Router runs searchProducts on the search subgraph.</v>
       </c>
-      <c r="I45" t="str">
+      <c r="J45" t="str">
         <v>Proposed</v>
       </c>
     </row>
@@ -32231,21 +32367,24 @@
         <v>Internal</v>
       </c>
       <c r="F46" t="str">
+        <v>Domain data mapping</v>
+      </c>
+      <c r="G46" t="str">
         <v>Index pipeline</v>
       </c>
-      <c r="G46" t="str">
+      <c r="H46" t="str">
         <v>Real-time</v>
       </c>
-      <c r="H46" t="str">
+      <c r="I46" t="str">
         <v>Emitted after (re)indexing a product document.</v>
       </c>
-      <c r="I46" t="str">
+      <c r="J46" t="str">
         <v>Proposed</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I46"/>
-  <dataValidations count="4">
+  <autoFilter ref="A1:J46"/>
+  <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" sqref="C2:C1000">
       <formula1>Applications!$A$2:$A$1000</formula1>
     </dataValidation>
@@ -32255,12 +32394,15 @@
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" sqref="E2:E1000">
       <formula1>"REST API,GraphQL,Kafka event,File (CSV),CDC,Internal"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" sqref="I2:I1000">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" sqref="F2:F1000">
+      <formula1>"API data mapping,Domain data mapping"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" sqref="J2:J1000">
       <formula1>"Draft,Proposed,Approved,Deprecated"</formula1>
     </dataValidation>
   </dataValidations>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I46"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J46"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -33576,7 +33718,7 @@
         <v>Applications</v>
       </c>
       <c r="B3" t="str">
-        <v>Step 1: every application with its domain and numbered AppType (01-Domain service … 08-Third party). AppID = APP-&lt;domain no&gt;-&lt;domain code&gt;-&lt;type no&gt;, e.g. APP-04-PRODT-01; a second app of the same type in the domain gets -02. A service owns its REST + GraphQL API, database and produced events.</v>
+        <v>Step 1: every application with its domain and numbered AppType (01-Domain service … 10-Data platform). AppID = APP-&lt;domain no&gt;-&lt;domain code&gt;-&lt;type no&gt;, e.g. APP-04-PRODT-01; a second app of the same type in the domain gets -02. A service owns its REST + GraphQL API, database and produced events.</v>
       </c>
     </row>
     <row r="4">
@@ -33616,7 +33758,7 @@
         <v>Flows</v>
       </c>
       <c r="B8" t="str">
-        <v>Integration flows between two applications with their pattern: REST API, GraphQL, Kafka event, File (CSV), CDC, or Internal (inside one application).</v>
+        <v>Integration flows between two applications with their pattern: REST API, GraphQL, Kafka event, File (CSV), CDC, or Internal (inside one application). MappingType: API data mapping = a call from the front end to the back end (front end → BFF / FedGQL router → domain / integration service → database or third party); Domain data mapping = a data sync (core → data hub → data platform, and the hub's subscribers). Left empty, it is filled in from the applications and pattern.</v>
       </c>
     </row>
     <row r="9">
@@ -33640,7 +33782,7 @@
         <v>Rules</v>
       </c>
       <c r="B11" t="str">
-        <v>Front ends integrate only via the BFF (REST) or the FedGQL router (GraphQL). Core / third-party systems feed integration services via REST API, Kafka event or File (CSV). Domain services expose REST / GraphQL over their own database and publish Kafka events.</v>
+        <v>Front ends integrate only via the BFF (REST) or the FedGQL router (GraphQL). Core / third-party systems feed integration services via REST API, Kafka event or File (CSV). Domain services expose REST / GraphQL over their own database and publish Kafka events. Data hubs (09) and data platforms (10) run on Databricks, Snowflake or ClickHouse and integrate via Kafka event (preferred), CDC, File (CSV) or REST API.</v>
       </c>
     </row>
     <row r="12">
